--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Dimensionamiento.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Dimensionamiento.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Criterios y método de dimens" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.1 Valores base de dimensionam" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.2 Proyección a 3 años (Caso 0" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.1 Usuarios y terminales concu" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2 TPS estimados (peor ventana" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.1 Cómputo — CD Talca (clúster" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.1 Cómputo — CD Talca (clúst_2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.2 Cómputo — Concepción (edge)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.3 Almacenamiento (ADR-10, RT-" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.4 Ancho de banda WAN por siti" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Dimensionamiento nube (ADR-1" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Plan de capacidad y crecimie" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Umbrales de desempeño (RT-09" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Primer cuello de botella (RT" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Pruebas de carga y estrés (" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. Referencias cruzadas con la" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. Trazabilidad normativa (res" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="1. Criterios y método de dimens" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2.1 Valores base de dimensionam" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2.2 Proyección a 3 años (Caso 0" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3.1 Usuarios y terminales concu" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3.2 TPS estimados (peor ventana" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4.1 Cómputo — CD Talca (clúster" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4.1 Cómputo — CD Talca (clúst_2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4.2 Cómputo — Concepción (edge)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="4.3 Almacenamiento (ADR-10, RT-" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="4.4 Ancho de banda WAN por siti" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5. Dimensionamiento nube (ADR-1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6. Plan de capacidad y crecimie" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7. Umbrales de desempeño (RT-09" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8. Primer cuello de botella (RT" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="10. Pruebas de carga y estrés (" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="12. Referencias cruzadas con la" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="13. Trazabilidad normativa (res" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -703,7 +703,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ECS Fargate Django (tareas 2 vCPU / 4 GB)</t>
+          <t>ECS Fargate, perfil de API PHP-FPM (tareas 1 vCPU / 2 GB)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -713,34 +713,34 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>6 (3×)</t>
+          <t>4; techo 8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Target Tracking CPU &gt; 70 %</t>
+          <t>Procesos PHP-FPM ocupados &gt; 70 %</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ECS Fargate Celery workers (2 vCPU / 4 GB)</t>
+          <t>ECS Fargate, consumidor de reconciliación y trabajos de Laravel (1 vCPU / 2 GB)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 + 2</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4 (2×)</t>
+          <t>4 + 4; erp-sync fijo en 2 procesos</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Cola (queue depth) / CPU</t>
+          <t>Edad del mensaje más antiguo / profundidad de cada cola</t>
         </is>
       </c>
     </row>
